--- a/reports/telegram/aegis_daily_2026-09-01.xlsx
+++ b/reports/telegram/aegis_daily_2026-09-01.xlsx
@@ -733,12 +733,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>R2-GNFC-IND-20260806-abf3d2</t>
+          <t>R2-PLTR-USA-20260810-caa9a7</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>GNFC_IND_20260806</t>
+          <t>PLTR_USA_20260810</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -748,7 +748,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>INDIA</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -758,7 +758,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>GNFC</t>
+          <t>PLTR</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr"/>
@@ -775,7 +775,7 @@
       <c r="L2" s="3" t="inlineStr"/>
       <c r="M2" s="3" t="inlineStr"/>
       <c r="N2" s="3" t="n">
-        <v>80.8</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="O2" s="3" t="inlineStr">
         <is>
@@ -783,24 +783,24 @@
         </is>
       </c>
       <c r="P2" s="3" t="n">
-        <v>34.1</v>
+        <v>48.2</v>
       </c>
       <c r="Q2" s="3" t="n">
-        <v>0</v>
+        <v>-0.8</v>
       </c>
       <c r="R2" s="3" t="inlineStr">
         <is>
-          <t>FOMC Rate Decision in 0d (high) (+63 more) → -2.5pts · crude +19.8% (rising) → +1.0pts</t>
+          <t>FOMC Rate Decision in 0d (high) (+35 more) → -2.5pts · crude +19.8% (rising) → +1.0pts</t>
         </is>
       </c>
       <c r="S2" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-1.0%) · Rank #1 · Conf 34% · band HOLD→STRONG · 22d left · → STRONG BUY</t>
+          <t>🟢 BUY (Δ-1.0%) · Rank #1 · Conf 49% · band STRONG · 17d left · → STRONG BUY</t>
         </is>
       </c>
       <c r="T2" s="3" t="inlineStr"/>
       <c r="U2" s="3" t="n">
-        <v>34.1</v>
+        <v>48.9</v>
       </c>
       <c r="V2" s="3" t="inlineStr">
         <is>
@@ -808,73 +808,73 @@
         </is>
       </c>
       <c r="W2" s="3" t="n">
-        <v>32.2</v>
+        <v>42.3</v>
       </c>
       <c r="X2" s="3" t="n">
         <v>1</v>
       </c>
       <c r="Y2" s="3" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="Z2" s="3" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="AA2" s="3" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="AB2" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="AC2" s="3" t="n">
-        <v>571.9</v>
+        <v>186.38</v>
       </c>
       <c r="AD2" s="3" t="n">
-        <v>553.3</v>
+        <v>186.38</v>
       </c>
       <c r="AE2" s="3" t="n">
-        <v>566.1799999999999</v>
+        <v>184.52</v>
       </c>
       <c r="AF2" s="3" t="n">
-        <v>577.62</v>
+        <v>188.24</v>
       </c>
       <c r="AG2" s="3" t="n">
-        <v>537.59</v>
+        <v>175.2</v>
       </c>
       <c r="AH2" s="3" t="n">
-        <v>-2.84</v>
+        <v>-6</v>
       </c>
       <c r="AI2" s="3" t="n">
-        <v>640.53</v>
+        <v>208.75</v>
       </c>
       <c r="AJ2" s="3" t="n">
-        <v>15.77</v>
+        <v>12</v>
       </c>
       <c r="AK2" s="3" t="n">
-        <v>709.16</v>
+        <v>231.11</v>
       </c>
       <c r="AL2" s="3" t="n">
-        <v>28.17</v>
+        <v>24</v>
       </c>
       <c r="AM2" s="3" t="n">
-        <v>582.55</v>
+        <v>186.29</v>
       </c>
       <c r="AN2" s="3" t="n">
-        <v>-1.83</v>
+        <v>0.05</v>
       </c>
       <c r="AO2" s="3" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="AP2" s="3" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="AQ2" s="3" t="n">
         <v>0</v>
       </c>
       <c r="AR2" s="3" t="inlineStr">
         <is>
-          <t>Value · Growth · Ai Hybrid</t>
+          <t>Value · Quality · Momentum</t>
         </is>
       </c>
       <c r="AS2" s="3" t="inlineStr"/>
@@ -886,19 +886,19 @@
       </c>
       <c r="AV2" s="3" t="inlineStr">
         <is>
-          <t>2026-09-01 00:48</t>
+          <t>2026-09-01 12:33</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>R1-ICICIBANK-IND-20260804-bfcaee</t>
+          <t>R2-MU-USA-20260901-d2af60</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>ICICIBANK_IND_20260804</t>
+          <t>MU_USA_20260901</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -908,53 +908,65 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>INDIA</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>ICICIBANK</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="inlineStr">
-        <is>
-          <t>ICICI Bank</t>
-        </is>
-      </c>
+          <t>MU</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr"/>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>STRONG BUY</t>
-        </is>
-      </c>
-      <c r="I3" s="3" t="inlineStr"/>
-      <c r="J3" s="3" t="inlineStr"/>
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>→ PLTR · +11.6pp alpha</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="K3" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="L3" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="M3" s="3" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N3" s="3" t="inlineStr"/>
-      <c r="O3" s="3" t="inlineStr"/>
-      <c r="P3" s="3" t="inlineStr"/>
-      <c r="Q3" s="3" t="inlineStr"/>
-      <c r="R3" s="3" t="inlineStr"/>
+      <c r="L3" s="3" t="inlineStr"/>
+      <c r="M3" s="3" t="inlineStr"/>
+      <c r="N3" s="3" t="n">
+        <v>73.5</v>
+      </c>
+      <c r="O3" s="3" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="P3" s="3" t="n">
+        <v>48.1</v>
+      </c>
+      <c r="Q3" s="3" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="R3" s="3" t="inlineStr">
+        <is>
+          <t>FOMC Rate Decision in 0d (high) (+35 more) → -2.5pts · crude +19.8% (rising) → +1.0pts</t>
+        </is>
+      </c>
       <c r="S3" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-2.7%) · Rank ↑ 2→1 · Conf 84% · momentum → · 91d left · → STRONG BUY</t>
+          <t>🔴 AVOID · Rank #2 · Conf 49% · band HOLD · 60d left · → EXIT (rotate to PLTR)</t>
         </is>
       </c>
       <c r="T3" s="3" t="inlineStr"/>
       <c r="U3" s="3" t="n">
-        <v>84</v>
+        <v>48.9</v>
       </c>
       <c r="V3" s="3" t="inlineStr">
         <is>
@@ -962,95 +974,91 @@
         </is>
       </c>
       <c r="W3" s="3" t="n">
-        <v>79</v>
-      </c>
-      <c r="X3" s="3" t="inlineStr"/>
+        <v>30.7</v>
+      </c>
+      <c r="X3" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="Y3" s="3" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="Z3" s="3" t="n">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="AA3" s="3" t="n">
-        <v>91</v>
-      </c>
-      <c r="AB3" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
+        <v>60</v>
+      </c>
+      <c r="AB3" s="3" t="inlineStr"/>
       <c r="AC3" s="3" t="n">
-        <v>1422</v>
+        <v>958.73</v>
       </c>
       <c r="AD3" s="3" t="n">
-        <v>1438.5</v>
+        <v>958.73</v>
       </c>
       <c r="AE3" s="3" t="n">
-        <v>1383</v>
+        <v>949.14</v>
       </c>
       <c r="AF3" s="3" t="n">
-        <v>1461</v>
+        <v>968.3200000000001</v>
       </c>
       <c r="AG3" s="3" t="n">
-        <v>1350.9</v>
+        <v>901.21</v>
       </c>
       <c r="AH3" s="3" t="n">
-        <v>-6.09</v>
+        <v>-6</v>
       </c>
       <c r="AI3" s="3" t="n">
-        <v>1498</v>
+        <v>1073.78</v>
       </c>
       <c r="AJ3" s="3" t="n">
-        <v>4.14</v>
+        <v>12</v>
       </c>
       <c r="AK3" s="3" t="n">
-        <v>1602.86</v>
+        <v>1188.83</v>
       </c>
       <c r="AL3" s="3" t="n">
-        <v>11.43</v>
+        <v>24</v>
       </c>
       <c r="AM3" s="3" t="n">
-        <v>1432</v>
+        <v>932.86</v>
       </c>
       <c r="AN3" s="3" t="n">
-        <v>-0.7</v>
-      </c>
-      <c r="AO3" s="3" t="n">
-        <v>-1.15</v>
-      </c>
+        <v>2.77</v>
+      </c>
+      <c r="AO3" s="3" t="inlineStr"/>
       <c r="AP3" s="3" t="n">
         <v>0</v>
       </c>
       <c r="AQ3" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="AR3" s="3" t="inlineStr"/>
-      <c r="AS3" s="3" t="inlineStr">
-        <is>
-          <t>Financials</t>
-        </is>
-      </c>
+      <c r="AR3" s="3" t="inlineStr">
+        <is>
+          <t>Growth · Quality · Mean Reversion</t>
+        </is>
+      </c>
+      <c r="AS3" s="3" t="inlineStr"/>
       <c r="AT3" s="3" t="n">
         <v>5</v>
       </c>
       <c r="AU3" s="3" t="n">
-        <v>4.14</v>
+        <v>11.6</v>
       </c>
       <c r="AV3" s="3" t="inlineStr">
         <is>
-          <t>2026-09-01 00:48</t>
+          <t>2026-09-01 12:33</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>R1-CIPLA-IND-20260828-cfb313</t>
+          <t>R2-HOOD-USA-20260901-754363</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>CIPLA_IND_20260828</t>
+          <t>HOOD_USA_20260901</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -1060,45 +1068,65 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>INDIA</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>CIPLA</t>
+          <t>HOOD</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr"/>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>STRONG BUY</t>
-        </is>
-      </c>
-      <c r="I4" s="3" t="inlineStr"/>
-      <c r="J4" s="3" t="inlineStr"/>
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>→ PLTR · +14.3pp alpha</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="K4" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L4" s="3" t="inlineStr"/>
       <c r="M4" s="3" t="inlineStr"/>
-      <c r="N4" s="3" t="inlineStr"/>
-      <c r="O4" s="3" t="inlineStr"/>
-      <c r="P4" s="3" t="inlineStr"/>
-      <c r="Q4" s="3" t="inlineStr"/>
-      <c r="R4" s="3" t="inlineStr"/>
+      <c r="N4" s="3" t="n">
+        <v>74.40000000000001</v>
+      </c>
+      <c r="O4" s="3" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="P4" s="3" t="n">
+        <v>48.2</v>
+      </c>
+      <c r="Q4" s="3" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="R4" s="3" t="inlineStr">
+        <is>
+          <t>FOMC Rate Decision in 0d (high) (+35 more) → -2.5pts · crude +19.8% (rising) → +1.0pts</t>
+        </is>
+      </c>
       <c r="S4" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-2.9%) · Rank #3 · Conf 73% · momentum → · 91d left · → STRONG BUY</t>
+          <t>🔴 AVOID · Rank #4 · Conf 49% · band HOLD · 60d left · → EXIT (rotate to PLTR)</t>
         </is>
       </c>
       <c r="T4" s="3" t="inlineStr"/>
       <c r="U4" s="3" t="n">
-        <v>73</v>
+        <v>48.9</v>
       </c>
       <c r="V4" s="3" t="inlineStr">
         <is>
@@ -1106,91 +1134,89 @@
         </is>
       </c>
       <c r="W4" s="3" t="n">
-        <v>67</v>
-      </c>
-      <c r="X4" s="3" t="inlineStr"/>
+        <v>28</v>
+      </c>
+      <c r="X4" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="Y4" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="AA4" s="3" t="n">
-        <v>91</v>
-      </c>
-      <c r="AB4" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
+        <v>60</v>
+      </c>
+      <c r="AB4" s="3" t="inlineStr"/>
       <c r="AC4" s="3" t="n">
-        <v>1419</v>
+        <v>104.81</v>
       </c>
       <c r="AD4" s="3" t="n">
-        <v>1413.5</v>
+        <v>104.81</v>
       </c>
       <c r="AE4" s="3" t="n">
-        <v>1377</v>
+        <v>103.76</v>
       </c>
       <c r="AF4" s="3" t="n">
-        <v>1461</v>
+        <v>105.86</v>
       </c>
       <c r="AG4" s="3" t="n">
-        <v>1348.05</v>
+        <v>99.56999999999999</v>
       </c>
       <c r="AH4" s="3" t="n">
-        <v>-4.63</v>
+        <v>-5</v>
       </c>
       <c r="AI4" s="3" t="n">
-        <v>1532.52</v>
+        <v>113.19</v>
       </c>
       <c r="AJ4" s="3" t="n">
-        <v>8.42</v>
+        <v>8</v>
       </c>
       <c r="AK4" s="3" t="n">
-        <v>1639.7964</v>
+        <v>120.53</v>
       </c>
       <c r="AL4" s="3" t="n">
-        <v>16.01</v>
+        <v>15</v>
       </c>
       <c r="AM4" s="3" t="n">
-        <v>1413.5</v>
+        <v>104.26</v>
       </c>
       <c r="AN4" s="3" t="n">
-        <v>0.39</v>
-      </c>
-      <c r="AO4" s="3" t="n">
-        <v>0.39</v>
-      </c>
-      <c r="AP4" s="3" t="inlineStr"/>
-      <c r="AQ4" s="3" t="inlineStr"/>
-      <c r="AR4" s="3" t="inlineStr"/>
-      <c r="AS4" s="3" t="inlineStr">
-        <is>
-          <t>Pharma</t>
-        </is>
-      </c>
-      <c r="AT4" s="3" t="n">
-        <v>5</v>
-      </c>
+        <v>0.53</v>
+      </c>
+      <c r="AO4" s="3" t="inlineStr"/>
+      <c r="AP4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR4" s="3" t="inlineStr">
+        <is>
+          <t>Momentum · Value · Mean Reversion</t>
+        </is>
+      </c>
+      <c r="AS4" s="3" t="inlineStr"/>
+      <c r="AT4" s="3" t="inlineStr"/>
       <c r="AU4" s="3" t="n">
-        <v>8.42</v>
+        <v>14.27</v>
       </c>
       <c r="AV4" s="3" t="inlineStr">
         <is>
-          <t>2026-09-01 00:48</t>
+          <t>2026-09-01 12:33</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>R1-BEL-IND-20260804-5cc411</t>
+          <t>R2-GRMN-USA-20260901-4fa3a5</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>BEL_IND_20260804</t>
+          <t>GRMN_USA_20260901</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -1200,53 +1226,65 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>INDIA</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>BEL</t>
-        </is>
-      </c>
-      <c r="G5" s="3" t="inlineStr">
-        <is>
-          <t>Bharat Electronics</t>
-        </is>
-      </c>
+          <t>GRMN</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr"/>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="I5" s="3" t="inlineStr"/>
-      <c r="J5" s="3" t="inlineStr"/>
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>→ PLTR · +14.9pp alpha</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="K5" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="L5" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="M5" s="3" t="n">
-        <v>-3</v>
-      </c>
-      <c r="N5" s="3" t="inlineStr"/>
-      <c r="O5" s="3" t="inlineStr"/>
-      <c r="P5" s="3" t="inlineStr"/>
-      <c r="Q5" s="3" t="inlineStr"/>
-      <c r="R5" s="3" t="inlineStr"/>
+      <c r="L5" s="3" t="inlineStr"/>
+      <c r="M5" s="3" t="inlineStr"/>
+      <c r="N5" s="3" t="n">
+        <v>72</v>
+      </c>
+      <c r="O5" s="3" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="P5" s="3" t="n">
+        <v>48.1</v>
+      </c>
+      <c r="Q5" s="3" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="R5" s="3" t="inlineStr">
+        <is>
+          <t>FOMC Rate Decision in 0d (high) (+35 more) → -2.5pts · crude +19.8% (rising) → +1.0pts</t>
+        </is>
+      </c>
       <c r="S5" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-3.0%) · Rank ↑ 8→5 · Conf 67% · momentum → · 91d left · → BUY</t>
+          <t>🔴 AVOID · Rank #5 · Conf 49% · band HOLD · 60d left · → EXIT (rotate to PLTR)</t>
         </is>
       </c>
       <c r="T5" s="3" t="inlineStr"/>
       <c r="U5" s="3" t="n">
-        <v>67</v>
+        <v>48.9</v>
       </c>
       <c r="V5" s="3" t="inlineStr">
         <is>
@@ -1254,95 +1292,89 @@
         </is>
       </c>
       <c r="W5" s="3" t="n">
-        <v>59</v>
-      </c>
-      <c r="X5" s="3" t="inlineStr"/>
+        <v>27.4</v>
+      </c>
+      <c r="X5" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="Y5" s="3" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="AA5" s="3" t="n">
-        <v>91</v>
-      </c>
-      <c r="AB5" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
+        <v>60</v>
+      </c>
+      <c r="AB5" s="3" t="inlineStr"/>
       <c r="AC5" s="3" t="n">
-        <v>406.6</v>
+        <v>284.11</v>
       </c>
       <c r="AD5" s="3" t="n">
-        <v>388.7</v>
+        <v>284.11</v>
       </c>
       <c r="AE5" s="3" t="n">
-        <v>395</v>
+        <v>281.27</v>
       </c>
       <c r="AF5" s="3" t="n">
-        <v>419</v>
+        <v>286.95</v>
       </c>
       <c r="AG5" s="3" t="n">
-        <v>386.27</v>
+        <v>269.9</v>
       </c>
       <c r="AH5" s="3" t="n">
-        <v>-0.63</v>
+        <v>-5</v>
       </c>
       <c r="AI5" s="3" t="n">
-        <v>439.128</v>
+        <v>306.84</v>
       </c>
       <c r="AJ5" s="3" t="n">
-        <v>12.97</v>
+        <v>8</v>
       </c>
       <c r="AK5" s="3" t="n">
-        <v>469.8669600000001</v>
+        <v>326.73</v>
       </c>
       <c r="AL5" s="3" t="n">
-        <v>20.88</v>
+        <v>15</v>
       </c>
       <c r="AM5" s="3" t="n">
-        <v>408.75</v>
+        <v>289.87</v>
       </c>
       <c r="AN5" s="3" t="n">
-        <v>-0.51</v>
-      </c>
-      <c r="AO5" s="3" t="n">
-        <v>4.61</v>
-      </c>
+        <v>-1.99</v>
+      </c>
+      <c r="AO5" s="3" t="inlineStr"/>
       <c r="AP5" s="3" t="n">
         <v>0</v>
       </c>
       <c r="AQ5" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="AR5" s="3" t="inlineStr"/>
-      <c r="AS5" s="3" t="inlineStr">
-        <is>
-          <t>Industrials</t>
-        </is>
-      </c>
-      <c r="AT5" s="3" t="n">
-        <v>5</v>
-      </c>
+      <c r="AR5" s="3" t="inlineStr">
+        <is>
+          <t>Quality · Mean Reversion · Trend</t>
+        </is>
+      </c>
+      <c r="AS5" s="3" t="inlineStr"/>
+      <c r="AT5" s="3" t="inlineStr"/>
       <c r="AU5" s="3" t="n">
-        <v>12.97</v>
+        <v>14.88</v>
       </c>
       <c r="AV5" s="3" t="inlineStr">
         <is>
-          <t>2026-09-01 00:48</t>
+          <t>2026-09-01 12:33</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>R1-ONGC-IND-20260811-f86a0f</t>
+          <t>R2-EXPD-USA-20260901-a811b5</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>ONGC_IND_20260811</t>
+          <t>EXPD_USA_20260901</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -1352,45 +1384,65 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>INDIA</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>ONGC</t>
+          <t>EXPD</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr"/>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="I6" s="3" t="inlineStr"/>
-      <c r="J6" s="3" t="inlineStr"/>
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>→ PLTR · +14.9pp alpha</t>
+        </is>
+      </c>
+      <c r="J6" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="K6" s="3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L6" s="3" t="inlineStr"/>
       <c r="M6" s="3" t="inlineStr"/>
-      <c r="N6" s="3" t="inlineStr"/>
-      <c r="O6" s="3" t="inlineStr"/>
-      <c r="P6" s="3" t="inlineStr"/>
-      <c r="Q6" s="3" t="inlineStr"/>
-      <c r="R6" s="3" t="inlineStr"/>
+      <c r="N6" s="3" t="n">
+        <v>83.40000000000001</v>
+      </c>
+      <c r="O6" s="3" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="P6" s="3" t="n">
+        <v>48.1</v>
+      </c>
+      <c r="Q6" s="3" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="R6" s="3" t="inlineStr">
+        <is>
+          <t>FOMC Rate Decision in 0d (high) (+35 more) → -2.5pts · crude +19.8% (rising) → +1.0pts</t>
+        </is>
+      </c>
       <c r="S6" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-3.1%) · Rank #7 · Conf 67% · momentum → · 91d left · → BUY</t>
+          <t>🔴 AVOID · Rank #6 · Conf 49% · band STRONG · 60d left · → EXIT (rotate to PLTR)</t>
         </is>
       </c>
       <c r="T6" s="3" t="inlineStr"/>
       <c r="U6" s="3" t="n">
-        <v>67</v>
+        <v>48.9</v>
       </c>
       <c r="V6" s="3" t="inlineStr">
         <is>
@@ -1398,91 +1450,89 @@
         </is>
       </c>
       <c r="W6" s="3" t="n">
-        <v>53</v>
-      </c>
-      <c r="X6" s="3" t="inlineStr"/>
+        <v>27.4</v>
+      </c>
+      <c r="X6" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="Y6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z6" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="AA6" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="AB6" s="3" t="inlineStr"/>
+      <c r="AC6" s="3" t="n">
+        <v>189.65</v>
+      </c>
+      <c r="AD6" s="3" t="n">
+        <v>189.65</v>
+      </c>
+      <c r="AE6" s="3" t="n">
+        <v>187.75</v>
+      </c>
+      <c r="AF6" s="3" t="n">
+        <v>191.55</v>
+      </c>
+      <c r="AG6" s="3" t="n">
+        <v>180.17</v>
+      </c>
+      <c r="AH6" s="3" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AI6" s="3" t="n">
+        <v>204.82</v>
+      </c>
+      <c r="AJ6" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="AK6" s="3" t="n">
+        <v>218.1</v>
+      </c>
+      <c r="AL6" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="Z6" s="3" t="n">
-        <v>90</v>
-      </c>
-      <c r="AA6" s="3" t="n">
-        <v>91</v>
-      </c>
-      <c r="AB6" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="AC6" s="3" t="n">
-        <v>233.6</v>
-      </c>
-      <c r="AD6" s="3" t="n">
-        <v>239.4499969482422</v>
-      </c>
-      <c r="AE6" s="3" t="n">
-        <v>227</v>
-      </c>
-      <c r="AF6" s="3" t="n">
-        <v>241</v>
-      </c>
-      <c r="AG6" s="3" t="n">
-        <v>221.92</v>
-      </c>
-      <c r="AH6" s="3" t="n">
-        <v>-7.32</v>
-      </c>
-      <c r="AI6" s="3" t="n">
-        <v>252.288</v>
-      </c>
-      <c r="AJ6" s="3" t="n">
-        <v>5.36</v>
-      </c>
-      <c r="AK6" s="3" t="n">
-        <v>269.94816</v>
-      </c>
-      <c r="AL6" s="3" t="n">
-        <v>12.74</v>
-      </c>
       <c r="AM6" s="3" t="n">
-        <v>232.37</v>
+        <v>190.72</v>
       </c>
       <c r="AN6" s="3" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="AO6" s="3" t="n">
-        <v>-2.44</v>
-      </c>
-      <c r="AP6" s="3" t="inlineStr"/>
-      <c r="AQ6" s="3" t="inlineStr"/>
-      <c r="AR6" s="3" t="inlineStr"/>
-      <c r="AS6" s="3" t="inlineStr">
-        <is>
-          <t>Energy</t>
-        </is>
-      </c>
-      <c r="AT6" s="3" t="n">
-        <v>5</v>
-      </c>
+        <v>-0.5600000000000001</v>
+      </c>
+      <c r="AO6" s="3" t="inlineStr"/>
+      <c r="AP6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR6" s="3" t="inlineStr">
+        <is>
+          <t>Trend · Momentum · Growth</t>
+        </is>
+      </c>
+      <c r="AS6" s="3" t="inlineStr"/>
+      <c r="AT6" s="3" t="inlineStr"/>
       <c r="AU6" s="3" t="n">
-        <v>5.36</v>
+        <v>14.94</v>
       </c>
       <c r="AV6" s="3" t="inlineStr">
         <is>
-          <t>2026-09-01 00:48</t>
+          <t>2026-09-01 12:33</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>R1-IRCTC-IND-20260804-9c1ab0</t>
+          <t>R2-FTNT-USA-20260901-ac5de9</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>IRCTC_IND_20260804</t>
+          <t>FTNT_USA_20260901</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -1492,53 +1542,65 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>INDIA</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>IRCTC</t>
-        </is>
-      </c>
-      <c r="G7" s="3" t="inlineStr">
-        <is>
-          <t>IRCTC</t>
-        </is>
-      </c>
+          <t>FTNT</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr"/>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="I7" s="3" t="inlineStr"/>
-      <c r="J7" s="3" t="inlineStr"/>
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>→ PLTR · +15.1pp alpha</t>
+        </is>
+      </c>
+      <c r="J7" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="K7" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="L7" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="M7" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="N7" s="3" t="inlineStr"/>
-      <c r="O7" s="3" t="inlineStr"/>
-      <c r="P7" s="3" t="inlineStr"/>
-      <c r="Q7" s="3" t="inlineStr"/>
-      <c r="R7" s="3" t="inlineStr"/>
+      <c r="L7" s="3" t="inlineStr"/>
+      <c r="M7" s="3" t="inlineStr"/>
+      <c r="N7" s="3" t="n">
+        <v>77.59999999999999</v>
+      </c>
+      <c r="O7" s="3" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="P7" s="3" t="n">
+        <v>45.5</v>
+      </c>
+      <c r="Q7" s="3" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="R7" s="3" t="inlineStr">
+        <is>
+          <t>FOMC Rate Decision in 0d (high) (+35 more) → -2.5pts · crude +19.8% (rising) → +1.0pts</t>
+        </is>
+      </c>
       <c r="S7" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-2.7%) · Rank ↓ 7→9 · Conf 67% · momentum → · 91d left · → HOLD</t>
+          <t>🔴 AVOID · Rank #7 · Conf 46% · band HOLD · 60d left · → EXIT (rotate to PLTR)</t>
         </is>
       </c>
       <c r="T7" s="3" t="inlineStr"/>
       <c r="U7" s="3" t="n">
-        <v>67</v>
+        <v>46.2</v>
       </c>
       <c r="V7" s="3" t="inlineStr">
         <is>
@@ -1546,95 +1608,89 @@
         </is>
       </c>
       <c r="W7" s="3" t="n">
-        <v>53</v>
-      </c>
-      <c r="X7" s="3" t="inlineStr"/>
+        <v>27.2</v>
+      </c>
+      <c r="X7" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="Y7" s="3" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="AA7" s="3" t="n">
-        <v>91</v>
-      </c>
-      <c r="AB7" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
+        <v>60</v>
+      </c>
+      <c r="AB7" s="3" t="inlineStr"/>
       <c r="AC7" s="3" t="n">
-        <v>482.4</v>
+        <v>170.93</v>
       </c>
       <c r="AD7" s="3" t="n">
-        <v>494.35</v>
+        <v>170.93</v>
       </c>
       <c r="AE7" s="3" t="n">
-        <v>469</v>
+        <v>169.22</v>
       </c>
       <c r="AF7" s="3" t="n">
-        <v>496</v>
+        <v>172.64</v>
       </c>
       <c r="AG7" s="3" t="n">
-        <v>458.28</v>
+        <v>162.38</v>
       </c>
       <c r="AH7" s="3" t="n">
-        <v>-7.3</v>
+        <v>-5</v>
       </c>
       <c r="AI7" s="3" t="n">
-        <v>520.992</v>
+        <v>184.6</v>
       </c>
       <c r="AJ7" s="3" t="n">
-        <v>5.39</v>
+        <v>8</v>
       </c>
       <c r="AK7" s="3" t="n">
-        <v>557.46144</v>
+        <v>196.57</v>
       </c>
       <c r="AL7" s="3" t="n">
-        <v>12.77</v>
+        <v>15</v>
       </c>
       <c r="AM7" s="3" t="n">
-        <v>486.75</v>
+        <v>172.78</v>
       </c>
       <c r="AN7" s="3" t="n">
-        <v>-0.89</v>
-      </c>
-      <c r="AO7" s="3" t="n">
-        <v>-2.42</v>
-      </c>
+        <v>-1.07</v>
+      </c>
+      <c r="AO7" s="3" t="inlineStr"/>
       <c r="AP7" s="3" t="n">
         <v>0</v>
       </c>
       <c r="AQ7" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="AR7" s="3" t="inlineStr"/>
-      <c r="AS7" s="3" t="inlineStr">
-        <is>
-          <t>Transport</t>
-        </is>
-      </c>
-      <c r="AT7" s="3" t="n">
-        <v>5</v>
-      </c>
+      <c r="AR7" s="3" t="inlineStr">
+        <is>
+          <t>Quality · Value · Growth</t>
+        </is>
+      </c>
+      <c r="AS7" s="3" t="inlineStr"/>
+      <c r="AT7" s="3" t="inlineStr"/>
       <c r="AU7" s="3" t="n">
-        <v>5.39</v>
+        <v>15.06</v>
       </c>
       <c r="AV7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-01 00:48</t>
+          <t>2026-09-01 12:33</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>R1-DABUR-IND-20260828-284464</t>
+          <t>R2-VLO-USA-20260901-a27a3c</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>DABUR_IND_20260828</t>
+          <t>VLO_USA_20260901</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1644,45 +1700,65 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>INDIA</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>DABUR</t>
+          <t>VLO</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr"/>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="I8" s="3" t="inlineStr"/>
-      <c r="J8" s="3" t="inlineStr"/>
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>→ PLTR · +15.6pp alpha</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="K8" s="3" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="L8" s="3" t="inlineStr"/>
       <c r="M8" s="3" t="inlineStr"/>
-      <c r="N8" s="3" t="inlineStr"/>
-      <c r="O8" s="3" t="inlineStr"/>
-      <c r="P8" s="3" t="inlineStr"/>
-      <c r="Q8" s="3" t="inlineStr"/>
-      <c r="R8" s="3" t="inlineStr"/>
+      <c r="N8" s="3" t="n">
+        <v>78.7</v>
+      </c>
+      <c r="O8" s="3" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="P8" s="3" t="n">
+        <v>51</v>
+      </c>
+      <c r="Q8" s="3" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="R8" s="3" t="inlineStr">
+        <is>
+          <t>FOMC Rate Decision in 0d (high) (+35 more) → -2.5pts · crude +19.8% (rising) → +1.0pts</t>
+        </is>
+      </c>
       <c r="S8" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-3.1%) · Rank #10 · Conf 62% · momentum → · 91d left · → BUY</t>
+          <t>🔴 AVOID · Rank #8 · Conf 52% · band HOLD · 60d left · → EXIT (rotate to PLTR)</t>
         </is>
       </c>
       <c r="T8" s="3" t="inlineStr"/>
       <c r="U8" s="3" t="n">
-        <v>62</v>
+        <v>51.7</v>
       </c>
       <c r="V8" s="3" t="inlineStr">
         <is>
@@ -1690,91 +1766,89 @@
         </is>
       </c>
       <c r="W8" s="3" t="n">
-        <v>50</v>
-      </c>
-      <c r="X8" s="3" t="inlineStr"/>
+        <v>26.7</v>
+      </c>
+      <c r="X8" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="Y8" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z8" s="3" t="n">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="AA8" s="3" t="n">
-        <v>91</v>
-      </c>
-      <c r="AB8" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
+        <v>60</v>
+      </c>
+      <c r="AB8" s="3" t="inlineStr"/>
       <c r="AC8" s="3" t="n">
-        <v>382.8</v>
+        <v>358.92</v>
       </c>
       <c r="AD8" s="3" t="n">
-        <v>385.1499938964844</v>
+        <v>358.92</v>
       </c>
       <c r="AE8" s="3" t="n">
-        <v>371</v>
+        <v>355.33</v>
       </c>
       <c r="AF8" s="3" t="n">
-        <v>395</v>
+        <v>362.51</v>
       </c>
       <c r="AG8" s="3" t="n">
-        <v>363.66</v>
+        <v>340.97</v>
       </c>
       <c r="AH8" s="3" t="n">
-        <v>-5.58</v>
+        <v>-5</v>
       </c>
       <c r="AI8" s="3" t="n">
-        <v>413.424</v>
+        <v>387.63</v>
       </c>
       <c r="AJ8" s="3" t="n">
-        <v>7.34</v>
+        <v>8</v>
       </c>
       <c r="AK8" s="3" t="n">
-        <v>442.36368</v>
+        <v>412.76</v>
       </c>
       <c r="AL8" s="3" t="n">
-        <v>14.85</v>
+        <v>15</v>
       </c>
       <c r="AM8" s="3" t="n">
-        <v>385.15</v>
+        <v>346.59</v>
       </c>
       <c r="AN8" s="3" t="n">
-        <v>-0.62</v>
-      </c>
-      <c r="AO8" s="3" t="n">
-        <v>-0.61</v>
-      </c>
-      <c r="AP8" s="3" t="inlineStr"/>
-      <c r="AQ8" s="3" t="inlineStr"/>
-      <c r="AR8" s="3" t="inlineStr"/>
-      <c r="AS8" s="3" t="inlineStr">
-        <is>
-          <t>FMCG</t>
-        </is>
-      </c>
-      <c r="AT8" s="3" t="n">
-        <v>5</v>
-      </c>
+        <v>3.56</v>
+      </c>
+      <c r="AO8" s="3" t="inlineStr"/>
+      <c r="AP8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR8" s="3" t="inlineStr">
+        <is>
+          <t>Growth · Trend · Momentum</t>
+        </is>
+      </c>
+      <c r="AS8" s="3" t="inlineStr"/>
+      <c r="AT8" s="3" t="inlineStr"/>
       <c r="AU8" s="3" t="n">
-        <v>7.34</v>
+        <v>15.58</v>
       </c>
       <c r="AV8" s="3" t="inlineStr">
         <is>
-          <t>2026-09-01 00:48</t>
+          <t>2026-09-01 12:33</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>R1-TATASTEEL-IND-20260828-9c799a</t>
+          <t>R2-KVUE-USA-20260901-bc1548</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>TATASTEEL_IND_20260828</t>
+          <t>KVUE_USA_20260901</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1784,45 +1858,65 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>INDIA</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>TATASTEEL</t>
+          <t>KVUE</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr"/>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="I9" s="3" t="inlineStr"/>
-      <c r="J9" s="3" t="inlineStr"/>
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>→ PLTR · +67.9pp alpha</t>
+        </is>
+      </c>
+      <c r="J9" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="K9" s="3" t="n">
         <v>11</v>
       </c>
       <c r="L9" s="3" t="inlineStr"/>
       <c r="M9" s="3" t="inlineStr"/>
-      <c r="N9" s="3" t="inlineStr"/>
-      <c r="O9" s="3" t="inlineStr"/>
-      <c r="P9" s="3" t="inlineStr"/>
-      <c r="Q9" s="3" t="inlineStr"/>
-      <c r="R9" s="3" t="inlineStr"/>
+      <c r="N9" s="3" t="n">
+        <v>52.5</v>
+      </c>
+      <c r="O9" s="3" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="P9" s="3" t="n">
+        <v>29.1</v>
+      </c>
+      <c r="Q9" s="3" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="R9" s="3" t="inlineStr">
+        <is>
+          <t>FOMC Rate Decision in 0d (high) (+35 more) → -2.5pts · crude +19.8% (rising) → +1.0pts</t>
+        </is>
+      </c>
       <c r="S9" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-3.0%) · Rank #11 · Conf 62% · momentum → · 91d left · → BUY</t>
+          <t>🔴 AVOID · Rank #11 · Conf 30% · band EXIT · 60d left · → EXIT (rotate to PLTR)</t>
         </is>
       </c>
       <c r="T9" s="3" t="inlineStr"/>
       <c r="U9" s="3" t="n">
-        <v>62</v>
+        <v>29.9</v>
       </c>
       <c r="V9" s="3" t="inlineStr">
         <is>
@@ -1830,91 +1924,89 @@
         </is>
       </c>
       <c r="W9" s="3" t="n">
-        <v>49</v>
-      </c>
-      <c r="X9" s="3" t="inlineStr"/>
+        <v>-25.6</v>
+      </c>
+      <c r="X9" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="Y9" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="AA9" s="3" t="n">
-        <v>91</v>
-      </c>
-      <c r="AB9" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
+        <v>60</v>
+      </c>
+      <c r="AB9" s="3" t="inlineStr"/>
       <c r="AC9" s="3" t="n">
-        <v>182.3</v>
+        <v>18.88</v>
       </c>
       <c r="AD9" s="3" t="n">
-        <v>187.4600067138672</v>
+        <v>18.88</v>
       </c>
       <c r="AE9" s="3" t="n">
-        <v>177</v>
+        <v>18.69</v>
       </c>
       <c r="AF9" s="3" t="n">
-        <v>188</v>
+        <v>19.07</v>
       </c>
       <c r="AG9" s="3" t="n">
-        <v>173.185</v>
+        <v>17.94</v>
       </c>
       <c r="AH9" s="3" t="n">
-        <v>-7.61</v>
+        <v>-4.98</v>
       </c>
       <c r="AI9" s="3" t="n">
-        <v>196.884</v>
+        <v>20.39</v>
       </c>
       <c r="AJ9" s="3" t="n">
-        <v>5.03</v>
+        <v>8</v>
       </c>
       <c r="AK9" s="3" t="n">
-        <v>210.66588</v>
+        <v>21.71</v>
       </c>
       <c r="AL9" s="3" t="n">
-        <v>12.38</v>
+        <v>14.99</v>
       </c>
       <c r="AM9" s="3" t="n">
-        <v>187.46</v>
+        <v>19.2</v>
       </c>
       <c r="AN9" s="3" t="n">
-        <v>-2.75</v>
-      </c>
-      <c r="AO9" s="3" t="n">
-        <v>-2.75</v>
-      </c>
-      <c r="AP9" s="3" t="inlineStr"/>
-      <c r="AQ9" s="3" t="inlineStr"/>
-      <c r="AR9" s="3" t="inlineStr"/>
-      <c r="AS9" s="3" t="inlineStr">
-        <is>
-          <t>Metal</t>
-        </is>
-      </c>
-      <c r="AT9" s="3" t="n">
-        <v>5</v>
-      </c>
+        <v>-1.67</v>
+      </c>
+      <c r="AO9" s="3" t="inlineStr"/>
+      <c r="AP9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR9" s="3" t="inlineStr">
+        <is>
+          <t>Adx 14 · Atr 14 Pct · Distance From 52W High Pct · Distance From 52W Low Pct · Earn Days To Next</t>
+        </is>
+      </c>
+      <c r="AS9" s="3" t="inlineStr"/>
+      <c r="AT9" s="3" t="inlineStr"/>
       <c r="AU9" s="3" t="n">
-        <v>5.03</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="AV9" s="3" t="inlineStr">
         <is>
-          <t>2026-09-01 00:48</t>
+          <t>2026-09-01 12:33</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>R2-CHAMBLFERT-IND-20260804-5eb424</t>
+          <t>R2-CBRE-USA-20260901-ffe84f</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>CHAMBLFERT_IND_20260804</t>
+          <t>CBRE_USA_20260901</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1924,7 +2016,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>INDIA</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1934,43 +2026,55 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>CHAMBLFERT</t>
-        </is>
-      </c>
-      <c r="G10" s="3" t="inlineStr">
-        <is>
-          <t>Chambal Fert.</t>
-        </is>
-      </c>
+          <t>CBRE</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr"/>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="I10" s="3" t="inlineStr"/>
-      <c r="J10" s="3" t="inlineStr"/>
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>→ PLTR · +68.0pp alpha</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="K10" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="L10" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="M10" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="N10" s="3" t="inlineStr"/>
-      <c r="O10" s="3" t="inlineStr"/>
-      <c r="P10" s="3" t="inlineStr"/>
-      <c r="Q10" s="3" t="inlineStr"/>
-      <c r="R10" s="3" t="inlineStr"/>
+        <v>12</v>
+      </c>
+      <c r="L10" s="3" t="inlineStr"/>
+      <c r="M10" s="3" t="inlineStr"/>
+      <c r="N10" s="3" t="n">
+        <v>52.5</v>
+      </c>
+      <c r="O10" s="3" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="P10" s="3" t="n">
+        <v>29.1</v>
+      </c>
+      <c r="Q10" s="3" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="R10" s="3" t="inlineStr">
+        <is>
+          <t>FOMC Rate Decision in 0d (high) (+35 more) → -2.5pts · crude +19.8% (rising) → +1.0pts</t>
+        </is>
+      </c>
       <c r="S10" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-1.0%) · Rank ↓ 3→8 · Conf 38% · momentum → · 61d left · → HOLD</t>
+          <t>🔴 AVOID · Rank #12 · Conf 30% · band EXIT · 60d left · → EXIT (rotate to PLTR)</t>
         </is>
       </c>
       <c r="T10" s="3" t="inlineStr"/>
       <c r="U10" s="3" t="n">
-        <v>38.3</v>
+        <v>29.9</v>
       </c>
       <c r="V10" s="3" t="inlineStr">
         <is>
@@ -1978,89 +2082,89 @@
         </is>
       </c>
       <c r="W10" s="3" t="n">
-        <v>22.4</v>
-      </c>
-      <c r="X10" s="3" t="inlineStr"/>
+        <v>-25.7</v>
+      </c>
+      <c r="X10" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="Y10" s="3" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="Z10" s="3" t="n">
         <v>60</v>
       </c>
       <c r="AA10" s="3" t="n">
-        <v>61</v>
-      </c>
-      <c r="AB10" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
+        <v>60</v>
+      </c>
+      <c r="AB10" s="3" t="inlineStr"/>
       <c r="AC10" s="3" t="n">
-        <v>443.35</v>
+        <v>145.81</v>
       </c>
       <c r="AD10" s="3" t="n">
-        <v>443.35</v>
+        <v>145.81</v>
       </c>
       <c r="AE10" s="3" t="n">
-        <v>438.92</v>
+        <v>144.35</v>
       </c>
       <c r="AF10" s="3" t="n">
-        <v>447.78</v>
+        <v>147.27</v>
       </c>
       <c r="AG10" s="3" t="n">
-        <v>421.1825</v>
+        <v>138.52</v>
       </c>
       <c r="AH10" s="3" t="n">
         <v>-5</v>
       </c>
       <c r="AI10" s="3" t="n">
-        <v>478.818</v>
+        <v>157.47</v>
       </c>
       <c r="AJ10" s="3" t="n">
         <v>8</v>
       </c>
       <c r="AK10" s="3" t="n">
-        <v>509.8525</v>
+        <v>167.68</v>
       </c>
       <c r="AL10" s="3" t="n">
         <v>15</v>
       </c>
       <c r="AM10" s="3" t="n">
-        <v>423.2</v>
+        <v>150.82</v>
       </c>
       <c r="AN10" s="3" t="n">
-        <v>-2.28</v>
-      </c>
-      <c r="AO10" s="3" t="n">
-        <v>0</v>
-      </c>
+        <v>-3.32</v>
+      </c>
+      <c r="AO10" s="3" t="inlineStr"/>
       <c r="AP10" s="3" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="AQ10" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="AR10" s="3" t="inlineStr"/>
+      <c r="AR10" s="3" t="inlineStr">
+        <is>
+          <t>Adx 14 · Atr 14 Pct · Distance From 52W High Pct · Distance From 52W Low Pct · Earn Days To Next</t>
+        </is>
+      </c>
       <c r="AS10" s="3" t="inlineStr"/>
       <c r="AT10" s="3" t="inlineStr"/>
       <c r="AU10" s="3" t="n">
-        <v>8</v>
+        <v>68.03</v>
       </c>
       <c r="AV10" s="3" t="inlineStr">
         <is>
-          <t>2026-09-01 00:48</t>
+          <t>2026-09-01 12:33</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>R2-PNB-IND-20260804-c7957c</t>
+          <t>R2-ESS-USA-20260901-82131a</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>PNB_IND_20260804</t>
+          <t>ESS_USA_20260901</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -2070,7 +2174,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>INDIA</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -2080,43 +2184,55 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>PNB</t>
-        </is>
-      </c>
-      <c r="G11" s="3" t="inlineStr">
-        <is>
-          <t>Punjab Natl. Bank</t>
-        </is>
-      </c>
+          <t>ESS</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr"/>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="I11" s="3" t="inlineStr"/>
-      <c r="J11" s="3" t="inlineStr"/>
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t>→ PLTR · +75.6pp alpha</t>
+        </is>
+      </c>
+      <c r="J11" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="K11" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="L11" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="M11" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" s="3" t="inlineStr"/>
-      <c r="O11" s="3" t="inlineStr"/>
-      <c r="P11" s="3" t="inlineStr"/>
-      <c r="Q11" s="3" t="inlineStr"/>
-      <c r="R11" s="3" t="inlineStr"/>
+        <v>15</v>
+      </c>
+      <c r="L11" s="3" t="inlineStr"/>
+      <c r="M11" s="3" t="inlineStr"/>
+      <c r="N11" s="3" t="n">
+        <v>52.5</v>
+      </c>
+      <c r="O11" s="3" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="P11" s="3" t="n">
+        <v>29.1</v>
+      </c>
+      <c r="Q11" s="3" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="R11" s="3" t="inlineStr">
+        <is>
+          <t>FOMC Rate Decision in 0d (high) (+35 more) → -2.5pts · crude +19.8% (rising) → +1.0pts</t>
+        </is>
+      </c>
       <c r="S11" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-1.0%) · Rank → 4→4 · Conf 32% · momentum → · 61d left · → HOLD</t>
+          <t>🔴 AVOID · Rank #15 · Conf 30% · band EXIT · 60d left · → EXIT (rotate to PLTR)</t>
         </is>
       </c>
       <c r="T11" s="3" t="inlineStr"/>
       <c r="U11" s="3" t="n">
-        <v>32.1</v>
+        <v>29.9</v>
       </c>
       <c r="V11" s="3" t="inlineStr">
         <is>
@@ -2124,89 +2240,89 @@
         </is>
       </c>
       <c r="W11" s="3" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="X11" s="3" t="inlineStr"/>
+        <v>-33.3</v>
+      </c>
+      <c r="X11" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="Y11" s="3" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="Z11" s="3" t="n">
         <v>60</v>
       </c>
       <c r="AA11" s="3" t="n">
-        <v>61</v>
-      </c>
-      <c r="AB11" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
+        <v>60</v>
+      </c>
+      <c r="AB11" s="3" t="inlineStr"/>
       <c r="AC11" s="3" t="n">
-        <v>113.36</v>
+        <v>282.96</v>
       </c>
       <c r="AD11" s="3" t="n">
-        <v>113.36</v>
+        <v>282.96</v>
       </c>
       <c r="AE11" s="3" t="n">
-        <v>112.23</v>
+        <v>280.13</v>
       </c>
       <c r="AF11" s="3" t="n">
-        <v>114.49</v>
+        <v>285.79</v>
       </c>
       <c r="AG11" s="3" t="n">
-        <v>107.692</v>
+        <v>268.81</v>
       </c>
       <c r="AH11" s="3" t="n">
         <v>-5</v>
       </c>
       <c r="AI11" s="3" t="n">
-        <v>122.4288</v>
+        <v>305.6</v>
       </c>
       <c r="AJ11" s="3" t="n">
         <v>8</v>
       </c>
       <c r="AK11" s="3" t="n">
-        <v>130.364</v>
+        <v>325.4</v>
       </c>
       <c r="AL11" s="3" t="n">
         <v>15</v>
       </c>
       <c r="AM11" s="3" t="n">
-        <v>115.2</v>
+        <v>280.76</v>
       </c>
       <c r="AN11" s="3" t="n">
-        <v>-1.62</v>
-      </c>
-      <c r="AO11" s="3" t="n">
-        <v>0</v>
-      </c>
+        <v>0.78</v>
+      </c>
+      <c r="AO11" s="3" t="inlineStr"/>
       <c r="AP11" s="3" t="n">
         <v>0</v>
       </c>
       <c r="AQ11" s="3" t="n">
-        <v>-2.01</v>
-      </c>
-      <c r="AR11" s="3" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="AR11" s="3" t="inlineStr">
+        <is>
+          <t>Adx 14 · Atr 14 Pct · Distance From 52W High Pct · Distance From 52W Low Pct · Earn Days To Next</t>
+        </is>
+      </c>
       <c r="AS11" s="3" t="inlineStr"/>
       <c r="AT11" s="3" t="inlineStr"/>
       <c r="AU11" s="3" t="n">
-        <v>8</v>
+        <v>75.59</v>
       </c>
       <c r="AV11" s="3" t="inlineStr">
         <is>
-          <t>2026-09-01 00:48</t>
+          <t>2026-09-01 12:33</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>R2-ITC-IND-20260804-a049df</t>
+          <t>R1-PLTR-USA-20260810-9c1c66</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>ITC_IND_20260804</t>
+          <t>PLTR_USA_20260810</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -2216,53 +2332,59 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>INDIA</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>R1</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>ITC</t>
-        </is>
-      </c>
-      <c r="G12" s="3" t="inlineStr">
-        <is>
-          <t>ITC</t>
-        </is>
-      </c>
+          <t>PLTR</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr"/>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="I12" s="3" t="inlineStr"/>
       <c r="J12" s="3" t="inlineStr"/>
       <c r="K12" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="L12" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="M12" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="N12" s="3" t="inlineStr"/>
-      <c r="O12" s="3" t="inlineStr"/>
-      <c r="P12" s="3" t="inlineStr"/>
-      <c r="Q12" s="3" t="inlineStr"/>
-      <c r="R12" s="3" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="L12" s="3" t="inlineStr"/>
+      <c r="M12" s="3" t="inlineStr"/>
+      <c r="N12" s="3" t="n">
+        <v>80.09999999999999</v>
+      </c>
+      <c r="O12" s="3" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="P12" s="3" t="n">
+        <v>48.2</v>
+      </c>
+      <c r="Q12" s="3" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="R12" s="3" t="inlineStr">
+        <is>
+          <t>FOMC Rate Decision in 0d (high) (+35 more) → -2.5pts · crude +19.8% (rising) → +1.0pts</t>
+        </is>
+      </c>
       <c r="S12" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-1.0%) · Rank ↓ 7→9 · Conf 38% · momentum → · 61d left · → HOLD</t>
+          <t>🟢 BUY (Δ-1.0%) · Rank #1 · Conf 49% · momentum → · band STRONG · 91d left · → BUY</t>
         </is>
       </c>
       <c r="T12" s="3" t="inlineStr"/>
       <c r="U12" s="3" t="n">
-        <v>38.3</v>
+        <v>48.9</v>
       </c>
       <c r="V12" s="3" t="inlineStr">
         <is>
@@ -2270,89 +2392,95 @@
         </is>
       </c>
       <c r="W12" s="3" t="n">
-        <v>21.6</v>
+        <v>66.5</v>
       </c>
       <c r="X12" s="3" t="inlineStr"/>
       <c r="Y12" s="3" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="Z12" s="3" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="AA12" s="3" t="n">
-        <v>61</v>
+        <v>91</v>
       </c>
       <c r="AB12" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="AC12" s="3" t="n">
-        <v>282.9</v>
+        <v>186.38</v>
       </c>
       <c r="AD12" s="3" t="n">
-        <v>282.9</v>
+        <v>186.38</v>
       </c>
       <c r="AE12" s="3" t="n">
-        <v>280.07</v>
+        <v>184.52</v>
       </c>
       <c r="AF12" s="3" t="n">
-        <v>285.73</v>
+        <v>188.24</v>
       </c>
       <c r="AG12" s="3" t="n">
-        <v>268.7549999999999</v>
+        <v>177.061</v>
       </c>
       <c r="AH12" s="3" t="n">
         <v>-5</v>
       </c>
       <c r="AI12" s="3" t="n">
-        <v>305.532</v>
+        <v>208.75</v>
       </c>
       <c r="AJ12" s="3" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AK12" s="3" t="n">
-        <v>325.3349999999999</v>
+        <v>223.3625</v>
       </c>
       <c r="AL12" s="3" t="n">
-        <v>15</v>
+        <v>19.84</v>
       </c>
       <c r="AM12" s="3" t="n">
-        <v>268.15</v>
+        <v>186.29</v>
       </c>
       <c r="AN12" s="3" t="n">
-        <v>-1.21</v>
+        <v>0.05</v>
       </c>
       <c r="AO12" s="3" t="n">
         <v>0</v>
       </c>
       <c r="AP12" s="3" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="AQ12" s="3" t="n">
         <v>0</v>
       </c>
       <c r="AR12" s="3" t="inlineStr"/>
-      <c r="AS12" s="3" t="inlineStr"/>
-      <c r="AT12" s="3" t="inlineStr"/>
+      <c r="AS12" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AT12" s="3" t="n">
+        <v>5</v>
+      </c>
       <c r="AU12" s="3" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AV12" s="3" t="inlineStr">
         <is>
-          <t>2026-09-01 00:48</t>
+          <t>2026-09-01 12:33</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>R2-BATAINDIA-IND-20260804-21b729</t>
+          <t>R1-GRMN-USA-20260901-f19c69</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>BATAINDIA_IND_20260804</t>
+          <t>GRMN_USA_20260901</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -2362,53 +2490,59 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>INDIA</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>R1</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>BATAINDIA</t>
-        </is>
-      </c>
-      <c r="G13" s="3" t="inlineStr">
-        <is>
-          <t>Bata India</t>
-        </is>
-      </c>
+          <t>GRMN</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr"/>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr"/>
       <c r="J13" s="3" t="inlineStr"/>
       <c r="K13" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="L13" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="M13" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" s="3" t="inlineStr"/>
-      <c r="O13" s="3" t="inlineStr"/>
-      <c r="P13" s="3" t="inlineStr"/>
-      <c r="Q13" s="3" t="inlineStr"/>
-      <c r="R13" s="3" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="L13" s="3" t="inlineStr"/>
+      <c r="M13" s="3" t="inlineStr"/>
+      <c r="N13" s="3" t="n">
+        <v>72</v>
+      </c>
+      <c r="O13" s="3" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="P13" s="3" t="n">
+        <v>48.1</v>
+      </c>
+      <c r="Q13" s="3" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="R13" s="3" t="inlineStr">
+        <is>
+          <t>FOMC Rate Decision in 0d (high) (+35 more) → -2.5pts · crude +19.8% (rising) → +1.0pts</t>
+        </is>
+      </c>
       <c r="S13" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-1.0%) · Rank → 15→15 · Conf 24% · momentum → · 61d left · → HOLD</t>
+          <t>🟢 BUY (Δ-2.0%) · Rank #2 · Conf 49% · momentum → · band HOLD · 91d left · → BUY</t>
         </is>
       </c>
       <c r="T13" s="3" t="inlineStr"/>
       <c r="U13" s="3" t="n">
-        <v>24</v>
+        <v>48.9</v>
       </c>
       <c r="V13" s="3" t="inlineStr">
         <is>
@@ -2416,58 +2550,58 @@
         </is>
       </c>
       <c r="W13" s="3" t="n">
-        <v>-30.3</v>
+        <v>50</v>
       </c>
       <c r="X13" s="3" t="inlineStr"/>
       <c r="Y13" s="3" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="Z13" s="3" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="AA13" s="3" t="n">
-        <v>61</v>
+        <v>91</v>
       </c>
       <c r="AB13" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="AC13" s="3" t="n">
-        <v>709</v>
+        <v>284.11</v>
       </c>
       <c r="AD13" s="3" t="n">
-        <v>709</v>
+        <v>284.11</v>
       </c>
       <c r="AE13" s="3" t="n">
-        <v>701.91</v>
+        <v>278.43</v>
       </c>
       <c r="AF13" s="3" t="n">
-        <v>716.09</v>
+        <v>289.79</v>
       </c>
       <c r="AG13" s="3" t="n">
-        <v>673.55</v>
+        <v>269.9045</v>
       </c>
       <c r="AH13" s="3" t="n">
         <v>-5</v>
       </c>
       <c r="AI13" s="3" t="n">
-        <v>765.72</v>
+        <v>306.8388</v>
       </c>
       <c r="AJ13" s="3" t="n">
         <v>8</v>
       </c>
       <c r="AK13" s="3" t="n">
-        <v>815.3499999999999</v>
+        <v>328.3175160000001</v>
       </c>
       <c r="AL13" s="3" t="n">
-        <v>15</v>
+        <v>15.56</v>
       </c>
       <c r="AM13" s="3" t="n">
-        <v>679.4</v>
+        <v>289.87</v>
       </c>
       <c r="AN13" s="3" t="n">
-        <v>-0.47</v>
+        <v>-1.99</v>
       </c>
       <c r="AO13" s="3" t="n">
         <v>0</v>
@@ -2476,29 +2610,35 @@
         <v>0</v>
       </c>
       <c r="AQ13" s="3" t="n">
-        <v>-1.5</v>
+        <v>0</v>
       </c>
       <c r="AR13" s="3" t="inlineStr"/>
-      <c r="AS13" s="3" t="inlineStr"/>
-      <c r="AT13" s="3" t="inlineStr"/>
+      <c r="AS13" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AT13" s="3" t="n">
+        <v>5</v>
+      </c>
       <c r="AU13" s="3" t="n">
         <v>8</v>
       </c>
       <c r="AV13" s="3" t="inlineStr">
         <is>
-          <t>2026-09-01 00:48</t>
+          <t>2026-09-01 12:33</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>R2-PERSISTENT-IND-20260805-48a8e2</t>
+          <t>R1-FTNT-USA-20260901-2a35fc</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>PERSISTENT_IND_20260805</t>
+          <t>FTNT_USA_20260901</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -2508,17 +2648,17 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>INDIA</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>R1</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>PERSISTENT</t>
+          <t>FTNT</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr"/>
@@ -2530,27 +2670,37 @@
       <c r="I14" s="3" t="inlineStr"/>
       <c r="J14" s="3" t="inlineStr"/>
       <c r="K14" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="L14" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="M14" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" s="3" t="inlineStr"/>
-      <c r="O14" s="3" t="inlineStr"/>
-      <c r="P14" s="3" t="inlineStr"/>
-      <c r="Q14" s="3" t="inlineStr"/>
-      <c r="R14" s="3" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="L14" s="3" t="inlineStr"/>
+      <c r="M14" s="3" t="inlineStr"/>
+      <c r="N14" s="3" t="n">
+        <v>77.59999999999999</v>
+      </c>
+      <c r="O14" s="3" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="P14" s="3" t="n">
+        <v>45.5</v>
+      </c>
+      <c r="Q14" s="3" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="R14" s="3" t="inlineStr">
+        <is>
+          <t>FOMC Rate Decision in 0d (high) (+35 more) → -2.5pts · crude +19.8% (rising) → +1.0pts</t>
+        </is>
+      </c>
       <c r="S14" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-1.0%) · Rank → 4→4 · Conf 41% · momentum → · 61d left · → HOLD</t>
+          <t>🟢 BUY (Δ-2.0%) · Rank #3 · Conf 46% · momentum → · band HOLD · 91d left · → HOLD</t>
         </is>
       </c>
       <c r="T14" s="3" t="inlineStr"/>
       <c r="U14" s="3" t="n">
-        <v>40.7</v>
+        <v>46.2</v>
       </c>
       <c r="V14" s="3" t="inlineStr">
         <is>
@@ -2558,89 +2708,95 @@
         </is>
       </c>
       <c r="W14" s="3" t="n">
-        <v>23.8</v>
+        <v>49.2</v>
       </c>
       <c r="X14" s="3" t="inlineStr"/>
       <c r="Y14" s="3" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="Z14" s="3" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="AA14" s="3" t="n">
-        <v>61</v>
+        <v>91</v>
       </c>
       <c r="AB14" s="3" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="AC14" s="3" t="n">
-        <v>5322.4</v>
+        <v>170.93</v>
       </c>
       <c r="AD14" s="3" t="n">
-        <v>5322.4</v>
+        <v>170.93</v>
       </c>
       <c r="AE14" s="3" t="n">
-        <v>5269.18</v>
+        <v>167.51</v>
       </c>
       <c r="AF14" s="3" t="n">
-        <v>5375.62</v>
+        <v>174.35</v>
       </c>
       <c r="AG14" s="3" t="n">
-        <v>5056.28</v>
+        <v>162.3835</v>
       </c>
       <c r="AH14" s="3" t="n">
         <v>-5</v>
       </c>
       <c r="AI14" s="3" t="n">
-        <v>5748.192</v>
+        <v>184.6044</v>
       </c>
       <c r="AJ14" s="3" t="n">
         <v>8</v>
       </c>
       <c r="AK14" s="3" t="n">
-        <v>6120.759999999999</v>
+        <v>197.526708</v>
       </c>
       <c r="AL14" s="3" t="n">
-        <v>15</v>
+        <v>15.56</v>
       </c>
       <c r="AM14" s="3" t="n">
-        <v>5791.5</v>
+        <v>172.78</v>
       </c>
       <c r="AN14" s="3" t="n">
-        <v>-2.87</v>
+        <v>-1.07</v>
       </c>
       <c r="AO14" s="3" t="n">
         <v>0</v>
       </c>
       <c r="AP14" s="3" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="AQ14" s="3" t="n">
         <v>0</v>
       </c>
       <c r="AR14" s="3" t="inlineStr"/>
-      <c r="AS14" s="3" t="inlineStr"/>
-      <c r="AT14" s="3" t="inlineStr"/>
+      <c r="AS14" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AT14" s="3" t="n">
+        <v>5</v>
+      </c>
       <c r="AU14" s="3" t="n">
         <v>8</v>
       </c>
       <c r="AV14" s="3" t="inlineStr">
         <is>
-          <t>2026-09-01 00:48</t>
+          <t>2026-09-01 12:33</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>R2-BAJAJHLDNG-IND-20260805-660791</t>
+          <t>R1-MU-USA-20260901-a967c0</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>BAJAJHLDNG_IND_20260805</t>
+          <t>MU_USA_20260901</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -2650,17 +2806,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>INDIA</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>R1</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>BAJAJHLDNG</t>
+          <t>MU</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr"/>
@@ -2672,27 +2828,37 @@
       <c r="I15" s="3" t="inlineStr"/>
       <c r="J15" s="3" t="inlineStr"/>
       <c r="K15" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="L15" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="M15" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" s="3" t="inlineStr"/>
-      <c r="O15" s="3" t="inlineStr"/>
-      <c r="P15" s="3" t="inlineStr"/>
-      <c r="Q15" s="3" t="inlineStr"/>
-      <c r="R15" s="3" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="L15" s="3" t="inlineStr"/>
+      <c r="M15" s="3" t="inlineStr"/>
+      <c r="N15" s="3" t="n">
+        <v>73.5</v>
+      </c>
+      <c r="O15" s="3" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="P15" s="3" t="n">
+        <v>48.1</v>
+      </c>
+      <c r="Q15" s="3" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="R15" s="3" t="inlineStr">
+        <is>
+          <t>FOMC Rate Decision in 0d (high) (+35 more) → -2.5pts · crude +19.8% (rising) → +1.0pts</t>
+        </is>
+      </c>
       <c r="S15" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-1.0%) · Rank → 10→10 · Conf 38% · momentum → · 61d left · → HOLD</t>
+          <t>🟢 BUY (Δ-1.0%) · Rank #4 · Conf 49% · momentum → · band HOLD · 91d left · → HOLD</t>
         </is>
       </c>
       <c r="T15" s="3" t="inlineStr"/>
       <c r="U15" s="3" t="n">
-        <v>38.3</v>
+        <v>48.9</v>
       </c>
       <c r="V15" s="3" t="inlineStr">
         <is>
@@ -2700,89 +2866,91 @@
         </is>
       </c>
       <c r="W15" s="3" t="n">
-        <v>20.7</v>
+        <v>49</v>
       </c>
       <c r="X15" s="3" t="inlineStr"/>
       <c r="Y15" s="3" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="Z15" s="3" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="AA15" s="3" t="n">
-        <v>61</v>
-      </c>
-      <c r="AB15" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
+        <v>91</v>
+      </c>
+      <c r="AB15" s="3" t="inlineStr"/>
       <c r="AC15" s="3" t="n">
-        <v>11127</v>
+        <v>958.73</v>
       </c>
       <c r="AD15" s="3" t="n">
-        <v>11127</v>
+        <v>958.73</v>
       </c>
       <c r="AE15" s="3" t="n">
-        <v>11015.73</v>
+        <v>949.14</v>
       </c>
       <c r="AF15" s="3" t="n">
-        <v>11238.27</v>
+        <v>968.3200000000001</v>
       </c>
       <c r="AG15" s="3" t="n">
-        <v>10570.65</v>
+        <v>910.7935</v>
       </c>
       <c r="AH15" s="3" t="n">
         <v>-5</v>
       </c>
       <c r="AI15" s="3" t="n">
-        <v>12017.16</v>
+        <v>1073.78</v>
       </c>
       <c r="AJ15" s="3" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AK15" s="3" t="n">
-        <v>12796.05</v>
+        <v>1148.9446</v>
       </c>
       <c r="AL15" s="3" t="n">
-        <v>15</v>
+        <v>19.84</v>
       </c>
       <c r="AM15" s="3" t="n">
-        <v>11361</v>
+        <v>932.86</v>
       </c>
       <c r="AN15" s="3" t="n">
-        <v>-0.25</v>
+        <v>2.77</v>
       </c>
       <c r="AO15" s="3" t="n">
         <v>0</v>
       </c>
       <c r="AP15" s="3" t="n">
-        <v>3.69</v>
+        <v>0</v>
       </c>
       <c r="AQ15" s="3" t="n">
         <v>0</v>
       </c>
       <c r="AR15" s="3" t="inlineStr"/>
-      <c r="AS15" s="3" t="inlineStr"/>
-      <c r="AT15" s="3" t="inlineStr"/>
+      <c r="AS15" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AT15" s="3" t="n">
+        <v>5</v>
+      </c>
       <c r="AU15" s="3" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AV15" s="3" t="inlineStr">
         <is>
-          <t>2026-09-01 00:48</t>
+          <t>2026-09-01 12:33</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>R2-LICI-IND-20260805-a4f409</t>
+          <t>R1-UBER-USA-20260810-2e9fcb</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>LICI_IND_20260805</t>
+          <t>UBER_USA_20260810</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -2792,17 +2960,17 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>INDIA</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>R1</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>LICI</t>
+          <t>UBER</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr"/>
@@ -2814,23 +2982,37 @@
       <c r="I16" s="3" t="inlineStr"/>
       <c r="J16" s="3" t="inlineStr"/>
       <c r="K16" s="3" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="L16" s="3" t="inlineStr"/>
       <c r="M16" s="3" t="inlineStr"/>
-      <c r="N16" s="3" t="inlineStr"/>
-      <c r="O16" s="3" t="inlineStr"/>
-      <c r="P16" s="3" t="inlineStr"/>
-      <c r="Q16" s="3" t="inlineStr"/>
-      <c r="R16" s="3" t="inlineStr"/>
+      <c r="N16" s="3" t="n">
+        <v>69.59999999999999</v>
+      </c>
+      <c r="O16" s="3" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="P16" s="3" t="n">
+        <v>50.9</v>
+      </c>
+      <c r="Q16" s="3" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="R16" s="3" t="inlineStr">
+        <is>
+          <t>FOMC Rate Decision in 0d (high) (+35 more) → -2.5pts · crude +19.8% (rising) → +1.0pts</t>
+        </is>
+      </c>
       <c r="S16" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-1.0%) · Rank #9 · Conf 37% · momentum → · 61d left · → HOLD</t>
+          <t>🟢 BUY (Δ-2.0%) · Rank #5 · Conf 52% · momentum → · band HOLD · 91d left · → HOLD</t>
         </is>
       </c>
       <c r="T16" s="3" t="inlineStr"/>
       <c r="U16" s="3" t="n">
-        <v>37.2</v>
+        <v>51.6</v>
       </c>
       <c r="V16" s="3" t="inlineStr">
         <is>
@@ -2838,58 +3020,58 @@
         </is>
       </c>
       <c r="W16" s="3" t="n">
-        <v>20.6</v>
+        <v>48</v>
       </c>
       <c r="X16" s="3" t="inlineStr"/>
       <c r="Y16" s="3" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="Z16" s="3" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="AA16" s="3" t="n">
-        <v>61</v>
+        <v>91</v>
       </c>
       <c r="AB16" s="3" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="AC16" s="3" t="n">
-        <v>391.3</v>
+        <v>75.65000000000001</v>
       </c>
       <c r="AD16" s="3" t="n">
-        <v>391.3</v>
+        <v>75.65000000000001</v>
       </c>
       <c r="AE16" s="3" t="n">
-        <v>387.39</v>
+        <v>74.14</v>
       </c>
       <c r="AF16" s="3" t="n">
-        <v>395.21</v>
+        <v>77.16</v>
       </c>
       <c r="AG16" s="3" t="n">
-        <v>371.735</v>
+        <v>71.86750000000001</v>
       </c>
       <c r="AH16" s="3" t="n">
         <v>-5</v>
       </c>
       <c r="AI16" s="3" t="n">
-        <v>422.604</v>
+        <v>81.70200000000001</v>
       </c>
       <c r="AJ16" s="3" t="n">
         <v>8</v>
       </c>
       <c r="AK16" s="3" t="n">
-        <v>449.995</v>
+        <v>87.42114000000002</v>
       </c>
       <c r="AL16" s="3" t="n">
-        <v>15</v>
+        <v>15.56</v>
       </c>
       <c r="AM16" s="3" t="n">
-        <v>411.4</v>
+        <v>76.95</v>
       </c>
       <c r="AN16" s="3" t="n">
-        <v>0.62</v>
+        <v>-1.69</v>
       </c>
       <c r="AO16" s="3" t="n">
         <v>0</v>
@@ -2901,26 +3083,32 @@
         <v>0</v>
       </c>
       <c r="AR16" s="3" t="inlineStr"/>
-      <c r="AS16" s="3" t="inlineStr"/>
-      <c r="AT16" s="3" t="inlineStr"/>
+      <c r="AS16" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AT16" s="3" t="n">
+        <v>5</v>
+      </c>
       <c r="AU16" s="3" t="n">
         <v>8</v>
       </c>
       <c r="AV16" s="3" t="inlineStr">
         <is>
-          <t>2026-09-01 00:48</t>
+          <t>2026-09-01 12:33</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>R2-TIINDIA-IND-20260805-44fbae</t>
+          <t>R1-HON-USA-20260901-df3a8a</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>TIINDIA_IND_20260805</t>
+          <t>HON_USA_20260901</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -2930,20 +3118,24 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>INDIA</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>R1</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>TIINDIA</t>
-        </is>
-      </c>
-      <c r="G17" s="3" t="inlineStr"/>
+          <t>HON</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t>Honeywell</t>
+        </is>
+      </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
           <t>HOLD</t>
@@ -2952,23 +3144,37 @@
       <c r="I17" s="3" t="inlineStr"/>
       <c r="J17" s="3" t="inlineStr"/>
       <c r="K17" s="3" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="L17" s="3" t="inlineStr"/>
       <c r="M17" s="3" t="inlineStr"/>
-      <c r="N17" s="3" t="inlineStr"/>
-      <c r="O17" s="3" t="inlineStr"/>
-      <c r="P17" s="3" t="inlineStr"/>
-      <c r="Q17" s="3" t="inlineStr"/>
-      <c r="R17" s="3" t="inlineStr"/>
+      <c r="N17" s="3" t="n">
+        <v>72.5</v>
+      </c>
+      <c r="O17" s="3" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="P17" s="3" t="n">
+        <v>53.8</v>
+      </c>
+      <c r="Q17" s="3" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="R17" s="3" t="inlineStr">
+        <is>
+          <t>FOMC Rate Decision in 0d (high) (+35 more) → -2.5pts · crude +19.8% (rising) → +1.0pts · 48 insider Form 4 filings last 90d → +2.0pts (note: buy/sell parse pending)</t>
+        </is>
+      </c>
       <c r="S17" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-1.0%) · Rank #12 · Conf 22% · momentum → · 61d left · → HOLD</t>
+          <t>🟢 BUY (Δ-2.0%) · Rank #6 · Conf 54% · momentum → · band HOLD · 91d left · → HOLD</t>
         </is>
       </c>
       <c r="T17" s="3" t="inlineStr"/>
       <c r="U17" s="3" t="n">
-        <v>21.5</v>
+        <v>54.5</v>
       </c>
       <c r="V17" s="3" t="inlineStr">
         <is>
@@ -2976,58 +3182,54 @@
         </is>
       </c>
       <c r="W17" s="3" t="n">
-        <v>-25.9</v>
+        <v>47.4</v>
       </c>
       <c r="X17" s="3" t="inlineStr"/>
       <c r="Y17" s="3" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="Z17" s="3" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="AA17" s="3" t="n">
-        <v>61</v>
-      </c>
-      <c r="AB17" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
+        <v>91</v>
+      </c>
+      <c r="AB17" s="3" t="inlineStr"/>
       <c r="AC17" s="3" t="n">
-        <v>2744.3</v>
+        <v>213.53</v>
       </c>
       <c r="AD17" s="3" t="n">
-        <v>2744.3</v>
+        <v>213.53</v>
       </c>
       <c r="AE17" s="3" t="n">
-        <v>2716.86</v>
+        <v>209.26</v>
       </c>
       <c r="AF17" s="3" t="n">
-        <v>2771.74</v>
+        <v>217.8</v>
       </c>
       <c r="AG17" s="3" t="n">
-        <v>2607.085</v>
+        <v>202.8535</v>
       </c>
       <c r="AH17" s="3" t="n">
         <v>-5</v>
       </c>
       <c r="AI17" s="3" t="n">
-        <v>2963.844000000001</v>
+        <v>230.6124</v>
       </c>
       <c r="AJ17" s="3" t="n">
         <v>8</v>
       </c>
       <c r="AK17" s="3" t="n">
-        <v>3155.945</v>
+        <v>246.755268</v>
       </c>
       <c r="AL17" s="3" t="n">
-        <v>15</v>
+        <v>15.56</v>
       </c>
       <c r="AM17" s="3" t="n">
-        <v>2852</v>
+        <v>217.43</v>
       </c>
       <c r="AN17" s="3" t="n">
-        <v>-2.67</v>
+        <v>-1.79</v>
       </c>
       <c r="AO17" s="3" t="n">
         <v>0</v>
@@ -3039,26 +3241,32 @@
         <v>0</v>
       </c>
       <c r="AR17" s="3" t="inlineStr"/>
-      <c r="AS17" s="3" t="inlineStr"/>
-      <c r="AT17" s="3" t="inlineStr"/>
+      <c r="AS17" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AT17" s="3" t="n">
+        <v>5</v>
+      </c>
       <c r="AU17" s="3" t="n">
         <v>8</v>
       </c>
       <c r="AV17" s="3" t="inlineStr">
         <is>
-          <t>2026-09-01 00:48</t>
+          <t>2026-09-01 12:33</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>R1-LUPIN-IND-20260805-6a4927</t>
+          <t>R1-MSFT-USA-20260810-673c2d</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>LUPIN_IND_20260805</t>
+          <t>MSFT_USA_20260810</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -3068,7 +3276,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>INDIA</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -3078,12 +3286,12 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>LUPIN</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>Lupin</t>
+          <t>Microsoft</t>
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr">
@@ -3094,16 +3302,12 @@
       <c r="I18" s="3" t="inlineStr"/>
       <c r="J18" s="3" t="inlineStr"/>
       <c r="K18" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="L18" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="M18" s="3" t="n">
-        <v>0</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="L18" s="3" t="inlineStr"/>
+      <c r="M18" s="3" t="inlineStr"/>
       <c r="N18" s="3" t="n">
-        <v>71.5</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="O18" s="3" t="inlineStr">
         <is>
@@ -3111,28 +3315,24 @@
         </is>
       </c>
       <c r="P18" s="3" t="n">
-        <v>40.6</v>
+        <v>51</v>
       </c>
       <c r="Q18" s="3" t="n">
-        <v>0</v>
+        <v>-0.8</v>
       </c>
       <c r="R18" s="3" t="inlineStr">
         <is>
-          <t>FOMC Rate Decision in 0d (high) (+63 more) → -2.5pts · crude +19.8% (rising) → +1.0pts</t>
+          <t>FOMC Rate Decision in 0d (high) (+35 more) → -2.5pts · crude +19.8% (rising) → +1.0pts · 33 insider Form 4 filings last 90d → +2.0pts (note: buy/sell parse pending)</t>
         </is>
       </c>
       <c r="S18" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-11.5%) · Rank → 3→3 · Conf 72% · momentum → · band HOLD · 61d left · → HOLD</t>
-        </is>
-      </c>
-      <c r="T18" s="3" t="inlineStr">
-        <is>
-          <t>CRITICAL·DEEP_LOSS·-10.6% ≤ -8.0% · EXIT URGENT</t>
-        </is>
-      </c>
+          <t>🟢 BUY (Δ-1.0%) · Rank #7 · Conf 52% · momentum → · band HOLD→STRONG · 91d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="T18" s="3" t="inlineStr"/>
       <c r="U18" s="3" t="n">
-        <v>72</v>
+        <v>51.7</v>
       </c>
       <c r="V18" s="3" t="inlineStr">
         <is>
@@ -3140,89 +3340,95 @@
         </is>
       </c>
       <c r="W18" s="3" t="n">
-        <v>71</v>
+        <v>47.2</v>
       </c>
       <c r="X18" s="3" t="inlineStr"/>
       <c r="Y18" s="3" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="Z18" s="3" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="AA18" s="3" t="n">
-        <v>61</v>
+        <v>91</v>
       </c>
       <c r="AB18" s="3" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="AC18" s="3" t="n">
-        <v>2160.2</v>
+        <v>507.29</v>
       </c>
       <c r="AD18" s="3" t="n">
-        <v>2417</v>
+        <v>507.29</v>
       </c>
       <c r="AE18" s="3" t="n">
-        <v>2392.83</v>
+        <v>502.22</v>
       </c>
       <c r="AF18" s="3" t="n">
-        <v>2441.17</v>
+        <v>512.36</v>
       </c>
       <c r="AG18" s="3" t="n">
-        <v>2296.15</v>
+        <v>481.9255</v>
       </c>
       <c r="AH18" s="3" t="n">
         <v>-5</v>
       </c>
       <c r="AI18" s="3" t="n">
-        <v>2610.36</v>
+        <v>568.16</v>
       </c>
       <c r="AJ18" s="3" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AK18" s="3" t="n">
-        <v>2779.55</v>
+        <v>607.9312</v>
       </c>
       <c r="AL18" s="3" t="n">
-        <v>15</v>
+        <v>19.84</v>
       </c>
       <c r="AM18" s="3" t="n">
-        <v>2159.6</v>
+        <v>513.53</v>
       </c>
       <c r="AN18" s="3" t="n">
-        <v>0.03</v>
+        <v>-1.22</v>
       </c>
       <c r="AO18" s="3" t="n">
-        <v>-10.62</v>
+        <v>0</v>
       </c>
       <c r="AP18" s="3" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AQ18" s="3" t="n">
-        <v>-10.62</v>
+        <v>0</v>
       </c>
       <c r="AR18" s="3" t="inlineStr"/>
-      <c r="AS18" s="3" t="inlineStr"/>
-      <c r="AT18" s="3" t="inlineStr"/>
+      <c r="AS18" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AT18" s="3" t="n">
+        <v>5</v>
+      </c>
       <c r="AU18" s="3" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AV18" s="3" t="inlineStr">
         <is>
-          <t>2026-09-01 00:48</t>
+          <t>2026-09-01 12:33</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>R1-PIDILITIND-IND-20260804-c2e1ef</t>
+          <t>R1-HOOD-USA-20260901-b01185</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>PIDILITIND_IND_20260804</t>
+          <t>HOOD_USA_20260901</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -3232,7 +3438,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>INDIA</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -3242,14 +3448,10 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>PIDILITIND</t>
-        </is>
-      </c>
-      <c r="G19" s="3" t="inlineStr">
-        <is>
-          <t>Pidilite</t>
-        </is>
-      </c>
+          <t>HOOD</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr"/>
       <c r="H19" s="3" t="inlineStr">
         <is>
           <t>HOLD</t>
@@ -3258,27 +3460,37 @@
       <c r="I19" s="3" t="inlineStr"/>
       <c r="J19" s="3" t="inlineStr"/>
       <c r="K19" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="L19" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="M19" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" s="3" t="inlineStr"/>
-      <c r="O19" s="3" t="inlineStr"/>
-      <c r="P19" s="3" t="inlineStr"/>
-      <c r="Q19" s="3" t="inlineStr"/>
-      <c r="R19" s="3" t="inlineStr"/>
+        <v>8</v>
+      </c>
+      <c r="L19" s="3" t="inlineStr"/>
+      <c r="M19" s="3" t="inlineStr"/>
+      <c r="N19" s="3" t="n">
+        <v>74.40000000000001</v>
+      </c>
+      <c r="O19" s="3" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="P19" s="3" t="n">
+        <v>48.2</v>
+      </c>
+      <c r="Q19" s="3" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="R19" s="3" t="inlineStr">
+        <is>
+          <t>FOMC Rate Decision in 0d (high) (+35 more) → -2.5pts · crude +19.8% (rising) → +1.0pts</t>
+        </is>
+      </c>
       <c r="S19" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-1.0%) · Rank → 3→3 · Conf 87% · momentum → · 61d left · → HOLD</t>
+          <t>🟢 BUY (Δ-2.0%) · Rank #8 · Conf 49% · momentum → · band HOLD · 91d left · → HOLD</t>
         </is>
       </c>
       <c r="T19" s="3" t="inlineStr"/>
       <c r="U19" s="3" t="n">
-        <v>87</v>
+        <v>48.9</v>
       </c>
       <c r="V19" s="3" t="inlineStr">
         <is>
@@ -3286,58 +3498,58 @@
         </is>
       </c>
       <c r="W19" s="3" t="n">
-        <v>71</v>
+        <v>44</v>
       </c>
       <c r="X19" s="3" t="inlineStr"/>
       <c r="Y19" s="3" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="Z19" s="3" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="AA19" s="3" t="n">
-        <v>61</v>
+        <v>91</v>
       </c>
       <c r="AB19" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="AC19" s="3" t="n">
-        <v>1625.5</v>
+        <v>104.81</v>
       </c>
       <c r="AD19" s="3" t="n">
-        <v>1625.5</v>
+        <v>104.81</v>
       </c>
       <c r="AE19" s="3" t="n">
-        <v>1609.24</v>
+        <v>102.71</v>
       </c>
       <c r="AF19" s="3" t="n">
-        <v>1641.76</v>
+        <v>106.91</v>
       </c>
       <c r="AG19" s="3" t="n">
-        <v>1544.225</v>
+        <v>99.56949999999999</v>
       </c>
       <c r="AH19" s="3" t="n">
         <v>-5</v>
       </c>
       <c r="AI19" s="3" t="n">
-        <v>1755.54</v>
+        <v>113.1948</v>
       </c>
       <c r="AJ19" s="3" t="n">
         <v>8</v>
       </c>
       <c r="AK19" s="3" t="n">
-        <v>1869.325</v>
+        <v>121.118436</v>
       </c>
       <c r="AL19" s="3" t="n">
-        <v>15</v>
+        <v>15.56</v>
       </c>
       <c r="AM19" s="3" t="n">
-        <v>1643.1</v>
+        <v>104.26</v>
       </c>
       <c r="AN19" s="3" t="n">
-        <v>-1.58</v>
+        <v>0.53</v>
       </c>
       <c r="AO19" s="3" t="n">
         <v>0</v>
@@ -3349,26 +3561,32 @@
         <v>0</v>
       </c>
       <c r="AR19" s="3" t="inlineStr"/>
-      <c r="AS19" s="3" t="inlineStr"/>
-      <c r="AT19" s="3" t="inlineStr"/>
+      <c r="AS19" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AT19" s="3" t="n">
+        <v>5</v>
+      </c>
       <c r="AU19" s="3" t="n">
         <v>8</v>
       </c>
       <c r="AV19" s="3" t="inlineStr">
         <is>
-          <t>2026-09-01 00:48</t>
+          <t>2026-09-01 12:33</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>R1-KOTAKBANK-IND-20260804-5087ff</t>
+          <t>R1-EXPD-USA-20260901-643782</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>KOTAKBANK_IND_20260804</t>
+          <t>EXPD_USA_20260901</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -3378,7 +3596,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>INDIA</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -3388,14 +3606,10 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>KOTAKBANK</t>
-        </is>
-      </c>
-      <c r="G20" s="3" t="inlineStr">
-        <is>
-          <t>Kotak Bank</t>
-        </is>
-      </c>
+          <t>EXPD</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr"/>
       <c r="H20" s="3" t="inlineStr">
         <is>
           <t>HOLD</t>
@@ -3404,27 +3618,37 @@
       <c r="I20" s="3" t="inlineStr"/>
       <c r="J20" s="3" t="inlineStr"/>
       <c r="K20" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="L20" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="M20" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" s="3" t="inlineStr"/>
-      <c r="O20" s="3" t="inlineStr"/>
-      <c r="P20" s="3" t="inlineStr"/>
-      <c r="Q20" s="3" t="inlineStr"/>
-      <c r="R20" s="3" t="inlineStr"/>
+        <v>9</v>
+      </c>
+      <c r="L20" s="3" t="inlineStr"/>
+      <c r="M20" s="3" t="inlineStr"/>
+      <c r="N20" s="3" t="n">
+        <v>83.40000000000001</v>
+      </c>
+      <c r="O20" s="3" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="P20" s="3" t="n">
+        <v>48.1</v>
+      </c>
+      <c r="Q20" s="3" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="R20" s="3" t="inlineStr">
+        <is>
+          <t>FOMC Rate Decision in 0d (high) (+35 more) → -2.5pts · crude +19.8% (rising) → +1.0pts</t>
+        </is>
+      </c>
       <c r="S20" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-1.0%) · Rank → 5→5 · Conf 71% · momentum → · 61d left · → HOLD</t>
+          <t>🟢 BUY (Δ-2.0%) · Rank #9 · Conf 49% · momentum → · band STRONG · 91d left · → HOLD</t>
         </is>
       </c>
       <c r="T20" s="3" t="inlineStr"/>
       <c r="U20" s="3" t="n">
-        <v>71</v>
+        <v>48.9</v>
       </c>
       <c r="V20" s="3" t="inlineStr">
         <is>
@@ -3432,58 +3656,58 @@
         </is>
       </c>
       <c r="W20" s="3" t="n">
-        <v>63</v>
+        <v>42.3</v>
       </c>
       <c r="X20" s="3" t="inlineStr"/>
       <c r="Y20" s="3" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="Z20" s="3" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="AA20" s="3" t="n">
-        <v>61</v>
+        <v>91</v>
       </c>
       <c r="AB20" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="AC20" s="3" t="n">
-        <v>389.3</v>
+        <v>189.65</v>
       </c>
       <c r="AD20" s="3" t="n">
-        <v>389.3</v>
+        <v>189.65</v>
       </c>
       <c r="AE20" s="3" t="n">
-        <v>385.41</v>
+        <v>185.86</v>
       </c>
       <c r="AF20" s="3" t="n">
-        <v>393.19</v>
+        <v>193.44</v>
       </c>
       <c r="AG20" s="3" t="n">
-        <v>369.835</v>
+        <v>180.1675</v>
       </c>
       <c r="AH20" s="3" t="n">
         <v>-5</v>
       </c>
       <c r="AI20" s="3" t="n">
-        <v>420.444</v>
+        <v>204.822</v>
       </c>
       <c r="AJ20" s="3" t="n">
         <v>8</v>
       </c>
       <c r="AK20" s="3" t="n">
-        <v>447.695</v>
+        <v>219.15954</v>
       </c>
       <c r="AL20" s="3" t="n">
-        <v>15</v>
+        <v>15.56</v>
       </c>
       <c r="AM20" s="3" t="n">
-        <v>423.95</v>
+        <v>190.72</v>
       </c>
       <c r="AN20" s="3" t="n">
-        <v>-0.27</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="AO20" s="3" t="n">
         <v>0</v>
@@ -3495,26 +3719,32 @@
         <v>0</v>
       </c>
       <c r="AR20" s="3" t="inlineStr"/>
-      <c r="AS20" s="3" t="inlineStr"/>
-      <c r="AT20" s="3" t="inlineStr"/>
+      <c r="AS20" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AT20" s="3" t="n">
+        <v>5</v>
+      </c>
       <c r="AU20" s="3" t="n">
         <v>8</v>
       </c>
       <c r="AV20" s="3" t="inlineStr">
         <is>
-          <t>2026-09-01 00:48</t>
+          <t>2026-09-01 12:33</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>R1-COALINDIA-IND-20260805-292818</t>
+          <t>R1-VLO-USA-20260901-952004</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>COALINDIA_IND_20260805</t>
+          <t>VLO_USA_20260901</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -3524,7 +3754,7 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>INDIA</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -3534,14 +3764,10 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>COALINDIA</t>
-        </is>
-      </c>
-      <c r="G21" s="3" t="inlineStr">
-        <is>
-          <t>Coal India</t>
-        </is>
-      </c>
+          <t>VLO</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr"/>
       <c r="H21" s="3" t="inlineStr">
         <is>
           <t>HOLD</t>
@@ -3552,14 +3778,10 @@
       <c r="K21" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="L21" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="M21" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="L21" s="3" t="inlineStr"/>
+      <c r="M21" s="3" t="inlineStr"/>
       <c r="N21" s="3" t="n">
-        <v>68.90000000000001</v>
+        <v>78.7</v>
       </c>
       <c r="O21" s="3" t="inlineStr">
         <is>
@@ -3567,24 +3789,24 @@
         </is>
       </c>
       <c r="P21" s="3" t="n">
-        <v>31.3</v>
+        <v>51</v>
       </c>
       <c r="Q21" s="3" t="n">
-        <v>0</v>
+        <v>-0.8</v>
       </c>
       <c r="R21" s="3" t="inlineStr">
         <is>
-          <t>FOMC Rate Decision in 0d (high) (+63 more) → -2.5pts · crude +19.8% (rising) → +1.0pts</t>
+          <t>FOMC Rate Decision in 0d (high) (+35 more) → -2.5pts · crude +19.8% (rising) → +1.0pts</t>
         </is>
       </c>
       <c r="S21" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-2.7%) · Rank → 10→10 · Conf 66% · momentum → · band HOLD · 61d left · → HOLD</t>
+          <t>🟢 BUY (Δ-2.0%) · Rank #10 · Conf 52% · momentum → · band HOLD · 91d left · → HOLD</t>
         </is>
       </c>
       <c r="T21" s="3" t="inlineStr"/>
       <c r="U21" s="3" t="n">
-        <v>66</v>
+        <v>51.7</v>
       </c>
       <c r="V21" s="3" t="inlineStr">
         <is>
@@ -3592,89 +3814,95 @@
         </is>
       </c>
       <c r="W21" s="3" t="n">
-        <v>50</v>
+        <v>40.3</v>
       </c>
       <c r="X21" s="3" t="inlineStr"/>
       <c r="Y21" s="3" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="Z21" s="3" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="AA21" s="3" t="n">
-        <v>61</v>
+        <v>91</v>
       </c>
       <c r="AB21" s="3" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="AC21" s="3" t="n">
-        <v>404.2</v>
+        <v>358.92</v>
       </c>
       <c r="AD21" s="3" t="n">
-        <v>411.3</v>
+        <v>358.92</v>
       </c>
       <c r="AE21" s="3" t="n">
-        <v>407.19</v>
+        <v>351.74</v>
       </c>
       <c r="AF21" s="3" t="n">
-        <v>415.41</v>
+        <v>366.1</v>
       </c>
       <c r="AG21" s="3" t="n">
-        <v>390.735</v>
+        <v>340.974</v>
       </c>
       <c r="AH21" s="3" t="n">
         <v>-5</v>
       </c>
       <c r="AI21" s="3" t="n">
-        <v>444.2040000000001</v>
+        <v>387.6336000000001</v>
       </c>
       <c r="AJ21" s="3" t="n">
         <v>8</v>
       </c>
       <c r="AK21" s="3" t="n">
-        <v>472.995</v>
+        <v>414.7679520000001</v>
       </c>
       <c r="AL21" s="3" t="n">
-        <v>15</v>
+        <v>15.56</v>
       </c>
       <c r="AM21" s="3" t="n">
-        <v>402.55</v>
+        <v>346.59</v>
       </c>
       <c r="AN21" s="3" t="n">
-        <v>0.41</v>
+        <v>3.56</v>
       </c>
       <c r="AO21" s="3" t="n">
-        <v>-1.73</v>
+        <v>0</v>
       </c>
       <c r="AP21" s="3" t="n">
         <v>0</v>
       </c>
       <c r="AQ21" s="3" t="n">
-        <v>-1.73</v>
+        <v>0</v>
       </c>
       <c r="AR21" s="3" t="inlineStr"/>
-      <c r="AS21" s="3" t="inlineStr"/>
-      <c r="AT21" s="3" t="inlineStr"/>
+      <c r="AS21" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AT21" s="3" t="n">
+        <v>5</v>
+      </c>
       <c r="AU21" s="3" t="n">
         <v>8</v>
       </c>
       <c r="AV21" s="3" t="inlineStr">
         <is>
-          <t>2026-09-01 00:48</t>
+          <t>2026-09-01 12:33</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>R1-BRITANNIA-IND-20260804-1de7ba</t>
+          <t>R2-TRV-USA-20260810-a2c57b</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>BRITANNIA_IND_20260804</t>
+          <t>TRV_USA_20260810</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -3684,20 +3912,24 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>INDIA</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>BRITANNIA</t>
-        </is>
-      </c>
-      <c r="G22" s="3" t="inlineStr"/>
+          <t>TRV</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr">
+        <is>
+          <t>Travelers</t>
+        </is>
+      </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
           <t>HOLD</t>
@@ -3706,10 +3938,10 @@
       <c r="I22" s="3" t="inlineStr"/>
       <c r="J22" s="3" t="inlineStr"/>
       <c r="K22" s="3" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="L22" s="3" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="M22" s="3" t="n">
         <v>0</v>
@@ -3721,12 +3953,12 @@
       <c r="R22" s="3" t="inlineStr"/>
       <c r="S22" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-1.0%) · Rank → 9→9 · Conf 66% · momentum → · 61d left · → HOLD</t>
+          <t>Rank → 1→1 · Conf 57% · momentum → · 61d left · → HOLD</t>
         </is>
       </c>
       <c r="T22" s="3" t="inlineStr"/>
       <c r="U22" s="3" t="n">
-        <v>66</v>
+        <v>56.8</v>
       </c>
       <c r="V22" s="3" t="inlineStr">
         <is>
@@ -3734,11 +3966,11 @@
         </is>
       </c>
       <c r="W22" s="3" t="n">
-        <v>52</v>
+        <v>29.2</v>
       </c>
       <c r="X22" s="3" t="inlineStr"/>
       <c r="Y22" s="3" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="Z22" s="3" t="n">
         <v>60</v>
@@ -3748,75 +3980,47 @@
       </c>
       <c r="AB22" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
-      <c r="AC22" s="3" t="n">
-        <v>5406</v>
-      </c>
-      <c r="AD22" s="3" t="n">
-        <v>5406</v>
-      </c>
-      <c r="AE22" s="3" t="n">
-        <v>5351.94</v>
-      </c>
-      <c r="AF22" s="3" t="n">
-        <v>5460.06</v>
-      </c>
-      <c r="AG22" s="3" t="n">
-        <v>5135.7</v>
-      </c>
-      <c r="AH22" s="3" t="n">
-        <v>-5</v>
-      </c>
-      <c r="AI22" s="3" t="n">
-        <v>5838.48</v>
-      </c>
-      <c r="AJ22" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="AK22" s="3" t="n">
-        <v>6216.9</v>
-      </c>
-      <c r="AL22" s="3" t="n">
-        <v>15</v>
-      </c>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="AC22" s="3" t="inlineStr"/>
+      <c r="AD22" s="3" t="inlineStr"/>
+      <c r="AE22" s="3" t="inlineStr"/>
+      <c r="AF22" s="3" t="inlineStr"/>
+      <c r="AG22" s="3" t="inlineStr"/>
+      <c r="AH22" s="3" t="inlineStr"/>
+      <c r="AI22" s="3" t="inlineStr"/>
+      <c r="AJ22" s="3" t="inlineStr"/>
+      <c r="AK22" s="3" t="inlineStr"/>
+      <c r="AL22" s="3" t="inlineStr"/>
       <c r="AM22" s="3" t="n">
-        <v>5323</v>
+        <v>369.33</v>
       </c>
       <c r="AN22" s="3" t="n">
-        <v>-1.28</v>
-      </c>
-      <c r="AO22" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP22" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ22" s="3" t="n">
-        <v>0</v>
-      </c>
+        <v>-0.92</v>
+      </c>
+      <c r="AO22" s="3" t="inlineStr"/>
+      <c r="AP22" s="3" t="inlineStr"/>
+      <c r="AQ22" s="3" t="inlineStr"/>
       <c r="AR22" s="3" t="inlineStr"/>
       <c r="AS22" s="3" t="inlineStr"/>
       <c r="AT22" s="3" t="inlineStr"/>
-      <c r="AU22" s="3" t="n">
-        <v>8</v>
-      </c>
+      <c r="AU22" s="3" t="inlineStr"/>
       <c r="AV22" s="3" t="inlineStr">
         <is>
-          <t>2026-09-01 00:48</t>
+          <t>2026-09-01 12:33</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>R1-TATAPOWER-IND-20260804-dafbb4</t>
+          <t>R2-V-USA-20260810-1697f4</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>TATAPOWER_IND_20260804</t>
+          <t>V_USA_20260810</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -3826,22 +4030,22 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>INDIA</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>TATAPOWER</t>
+          <t>V</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>Tata Power</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
@@ -3852,10 +4056,10 @@
       <c r="I23" s="3" t="inlineStr"/>
       <c r="J23" s="3" t="inlineStr"/>
       <c r="K23" s="3" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M23" s="3" t="n">
         <v>0</v>
@@ -3867,12 +4071,12 @@
       <c r="R23" s="3" t="inlineStr"/>
       <c r="S23" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-1.0%) · Rank → 6→6 · Conf 64% · momentum → · 61d left · → HOLD</t>
+          <t>Rank → 2→2 · Conf 54% · momentum → · 61d left · → HOLD</t>
         </is>
       </c>
       <c r="T23" s="3" t="inlineStr"/>
       <c r="U23" s="3" t="n">
-        <v>64</v>
+        <v>53.6</v>
       </c>
       <c r="V23" s="3" t="inlineStr">
         <is>
@@ -3880,11 +4084,11 @@
         </is>
       </c>
       <c r="W23" s="3" t="n">
-        <v>54</v>
+        <v>27.8</v>
       </c>
       <c r="X23" s="3" t="inlineStr"/>
       <c r="Y23" s="3" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="Z23" s="3" t="n">
         <v>60</v>
@@ -3894,63 +4098,35 @@
       </c>
       <c r="AB23" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
-      <c r="AC23" s="3" t="n">
-        <v>381.6</v>
-      </c>
-      <c r="AD23" s="3" t="n">
-        <v>381.6</v>
-      </c>
-      <c r="AE23" s="3" t="n">
-        <v>377.78</v>
-      </c>
-      <c r="AF23" s="3" t="n">
-        <v>385.42</v>
-      </c>
-      <c r="AG23" s="3" t="n">
-        <v>362.52</v>
-      </c>
-      <c r="AH23" s="3" t="n">
-        <v>-5</v>
-      </c>
-      <c r="AI23" s="3" t="n">
-        <v>412.128</v>
-      </c>
-      <c r="AJ23" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="AK23" s="3" t="n">
-        <v>438.84</v>
-      </c>
-      <c r="AL23" s="3" t="n">
-        <v>15</v>
-      </c>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="AC23" s="3" t="inlineStr"/>
+      <c r="AD23" s="3" t="inlineStr"/>
+      <c r="AE23" s="3" t="inlineStr"/>
+      <c r="AF23" s="3" t="inlineStr"/>
+      <c r="AG23" s="3" t="inlineStr"/>
+      <c r="AH23" s="3" t="inlineStr"/>
+      <c r="AI23" s="3" t="inlineStr"/>
+      <c r="AJ23" s="3" t="inlineStr"/>
+      <c r="AK23" s="3" t="inlineStr"/>
+      <c r="AL23" s="3" t="inlineStr"/>
       <c r="AM23" s="3" t="n">
-        <v>351.3</v>
+        <v>379.66</v>
       </c>
       <c r="AN23" s="3" t="n">
-        <v>-0.78</v>
-      </c>
-      <c r="AO23" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP23" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ23" s="3" t="n">
-        <v>0</v>
-      </c>
+        <v>-0.08</v>
+      </c>
+      <c r="AO23" s="3" t="inlineStr"/>
+      <c r="AP23" s="3" t="inlineStr"/>
+      <c r="AQ23" s="3" t="inlineStr"/>
       <c r="AR23" s="3" t="inlineStr"/>
       <c r="AS23" s="3" t="inlineStr"/>
       <c r="AT23" s="3" t="inlineStr"/>
-      <c r="AU23" s="3" t="n">
-        <v>8</v>
-      </c>
+      <c r="AU23" s="3" t="inlineStr"/>
       <c r="AV23" s="3" t="inlineStr">
         <is>
-          <t>2026-09-01 00:48</t>
+          <t>2026-09-01 12:33</t>
         </is>
       </c>
     </row>
